--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,491 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128471580</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>682467</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7092227</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128471181</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92648</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>682547</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7092122</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128471675</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>682349</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7092197</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128469259</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>682222</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7091995</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128469757</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>682385</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7092115</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,6 +1283,103 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128499442</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79702</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>683039</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7092240</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128471580</v>
       </c>
       <c r="B3" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128469259</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128469757</v>
       </c>
       <c r="B7" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128471580</v>
       </c>
       <c r="B3" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128469259</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128469757</v>
       </c>
       <c r="B7" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128499442</v>
       </c>
       <c r="B8" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128471580</v>
       </c>
       <c r="B3" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128469259</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128469757</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128499442</v>
       </c>
       <c r="B8" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128471580</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128469259</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128469757</v>
       </c>
       <c r="B7" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128499442</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128471580</v>
       </c>
       <c r="B3" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128469259</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128469757</v>
       </c>
       <c r="B7" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128499442</v>
       </c>
       <c r="B8" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128471580</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128469259</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128469757</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128499442</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128471580</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128471181</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128471675</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>128469259</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>128469757</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>128499442</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>128499442</v>
       </c>
       <c r="B8" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128499442</v>
+        <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>88928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,21 +1296,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683039</v>
+        <v>682364</v>
       </c>
       <c r="R8" t="n">
-        <v>7092240</v>
+        <v>7092183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,6 +1379,103 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128499442</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79653</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tosktjärnberget, Tosktjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>683039</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7092240</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88928</v>
+        <v>88930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88950</v>
+        <v>88952</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88952</v>
+        <v>88980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 14083-2021 artfynd.xlsx
+++ b/artfynd/A 14083-2021 artfynd.xlsx
@@ -1288,7 +1288,7 @@
         <v>129239902</v>
       </c>
       <c r="B8" t="n">
-        <v>88980</v>
+        <v>88986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
